--- a/samples/샘플_감독원양식_2026-09.xlsx
+++ b/samples/샘플_감독원양식_2026-09.xlsx
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>2822481204000</v>
+        <v>2822440031000</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2742798461000</v>
+        <v>2742784050000</v>
       </c>
     </row>
     <row r="16">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2720894604000</v>
+        <v>2720853431000</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2638508761000</v>
+        <v>2638494350000</v>
       </c>
     </row>
     <row r="17">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>407033104000</v>
+        <v>406991931000</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>395168861000</v>
+        <v>395154450000</v>
       </c>
     </row>
     <row r="20">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>357602096000</v>
+        <v>357643269000</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>345684239000</v>
+        <v>345698650000</v>
       </c>
     </row>
     <row r="23">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>294067896000</v>
+        <v>294109069000</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>281566039000</v>
+        <v>281580450000</v>
       </c>
     </row>
     <row r="25">
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1507074000</v>
+        <v>1474797000</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>15530253000</v>
+        <v>15236756300</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>14212403000</v>
+        <v>13949986950</v>
       </c>
     </row>
     <row r="11">
@@ -1094,87 +1094,108 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>기타사업비용</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>512659900</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>3174885400</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>2772781400</v>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>53000</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  재산관리비</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>32277000</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>293496700</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>262416050</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>법인세비용차감전순이익</t>
+          <t>기타사업비용</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>11248037100</v>
+        <v>542967400</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>107751697600</v>
+        <v>3395172010</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>113945893600</v>
+        <v>3061321615</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전순이익</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>2474568000</v>
+        <v>11185452600</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>23705373000</v>
+        <v>107237914290</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>25068097000</v>
+        <v>113394937335</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>법인세비용</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2460800000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>23592341000</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>24946887000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>90000</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>당기순이익</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>8773469100</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>84046324600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>88877796600</v>
+      <c r="C17" s="6" t="n">
+        <v>8724652600</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>83645573290</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>88448050335</v>
       </c>
     </row>
   </sheetData>
@@ -1297,7 +1318,7 @@
         <v>73961040000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>252741999000</v>
+        <v>252715962000</v>
       </c>
     </row>
     <row r="7">
@@ -1441,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-376543000</v>
+        <v>-375495000</v>
       </c>
     </row>
     <row r="11">
@@ -1513,7 +1534,7 @@
         <v>147922000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>631855000</v>
+        <v>631790000</v>
       </c>
     </row>
     <row r="13">
@@ -1549,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-2274678000</v>
+        <v>-2274444000</v>
       </c>
     </row>
     <row r="14">
@@ -1657,7 +1678,7 @@
         <v>73755360000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>252315345000</v>
+        <v>252290524000</v>
       </c>
     </row>
     <row r="17">
@@ -1693,7 +1714,7 @@
         <v>30817100000</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>101719595000</v>
+        <v>101709841000</v>
       </c>
     </row>
     <row r="18">
@@ -1837,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-134132000</v>
+        <v>-133778000</v>
       </c>
     </row>
     <row r="22">
@@ -1909,7 +1930,7 @@
         <v>61634000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>254299000</v>
+        <v>254275000</v>
       </c>
     </row>
     <row r="24">
@@ -1945,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-915476000</v>
+        <v>-915389000</v>
       </c>
     </row>
     <row r="25">
@@ -2053,7 +2074,7 @@
         <v>30731400000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>101834634000</v>
+        <v>101825297000</v>
       </c>
     </row>
     <row r="28">
@@ -2485,7 +2506,7 @@
         <v>16024892000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>52856818000</v>
+        <v>52849441000</v>
       </c>
     </row>
     <row r="40">
@@ -2629,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-105583000</v>
+        <v>-105269000</v>
       </c>
     </row>
     <row r="44">
@@ -2701,7 +2722,7 @@
         <v>32050000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>132142000</v>
+        <v>132124000</v>
       </c>
     </row>
     <row r="46">
@@ -2737,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-475711000</v>
+        <v>-475645000</v>
       </c>
     </row>
     <row r="47">
@@ -2845,7 +2866,7 @@
         <v>15980328000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>52883125000</v>
+        <v>52876110000</v>
       </c>
     </row>
   </sheetData>

--- a/samples/샘플_감독원양식_2026-09.xlsx
+++ b/samples/샘플_감독원양식_2026-09.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="재무상태표" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="손익계산서" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="보험계약부채변동" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무상태표" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="손익계산서" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보험계약부채변동" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/samples/샘플_감독원양식_2026-09.xlsx
+++ b/samples/샘플_감독원양식_2026-09.xlsx
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>2822440031000</v>
+        <v>2822858616000</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2742784050000</v>
+        <v>2742792258000</v>
       </c>
     </row>
     <row r="16">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2720853431000</v>
+        <v>2721272016000</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2638494350000</v>
+        <v>2638502558000</v>
       </c>
     </row>
     <row r="17">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>406991931000</v>
+        <v>407410516000</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>395154450000</v>
+        <v>395162658000</v>
       </c>
     </row>
     <row r="20">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>357643269000</v>
+        <v>357224684000</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>345698650000</v>
+        <v>345690442000</v>
       </c>
     </row>
     <row r="23">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>294109069000</v>
+        <v>293690484000</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>281580450000</v>
+        <v>281572242000</v>
       </c>
     </row>
     <row r="25">
@@ -1318,7 +1318,7 @@
         <v>73961040000</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>252715962000</v>
+        <v>252833754000</v>
       </c>
     </row>
     <row r="7">
@@ -1462,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-375495000</v>
+        <v>-225297000</v>
       </c>
     </row>
     <row r="11">
@@ -1534,7 +1534,7 @@
         <v>147922000</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>631790000</v>
+        <v>632084000</v>
       </c>
     </row>
     <row r="13">
@@ -1570,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-2274444000</v>
+        <v>-2275504000</v>
       </c>
     </row>
     <row r="14">
@@ -1678,7 +1678,7 @@
         <v>73755360000</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>252290524000</v>
+        <v>252557749000</v>
       </c>
     </row>
     <row r="17">
@@ -1714,7 +1714,7 @@
         <v>30817100000</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>101709841000</v>
+        <v>101744253000</v>
       </c>
     </row>
     <row r="18">
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-133778000</v>
+        <v>-80267000</v>
       </c>
     </row>
     <row r="22">
@@ -1930,7 +1930,7 @@
         <v>61634000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>254275000</v>
+        <v>254361000</v>
       </c>
     </row>
     <row r="24">
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>-915389000</v>
+        <v>-915698000</v>
       </c>
     </row>
     <row r="25">
@@ -2074,7 +2074,7 @@
         <v>30731400000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>101825297000</v>
+        <v>101912996000</v>
       </c>
     </row>
     <row r="28">
@@ -2506,7 +2506,7 @@
         <v>16024892000</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>52849441000</v>
+        <v>52871136000</v>
       </c>
     </row>
     <row r="40">
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-105269000</v>
+        <v>-63161000</v>
       </c>
     </row>
     <row r="44">
@@ -2722,7 +2722,7 @@
         <v>32050000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>132124000</v>
+        <v>132178000</v>
       </c>
     </row>
     <row r="46">
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>-475645000</v>
+        <v>-475840000</v>
       </c>
     </row>
     <row r="47">
@@ -2866,7 +2866,7 @@
         <v>15980328000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>52876110000</v>
+        <v>52939771000</v>
       </c>
     </row>
   </sheetData>
